--- a/output/pdf_financials_xlsx/TUF.xlsx
+++ b/output/pdf_financials_xlsx/TUF.xlsx
@@ -4236,16 +4236,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>1.363734</v>
+        <v>1.556586</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.363734</v>
+        <v>1.621019</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.479986</v>
+        <v>1.897779</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.622584</v>
+        <v>2.409574</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>3.088049</v>
@@ -10499,7 +10499,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -11067,7 +11071,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -12282,7 +12290,11 @@
           <t>Warrant Reserve (note 10)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -13355,7 +13367,11 @@
           <t>Warrant reserve (note 11)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="n">
         <v>0.192852</v>
       </c>

--- a/output/pdf_financials_xlsx/TUF.xlsx
+++ b/output/pdf_financials_xlsx/TUF.xlsx
@@ -849,16 +849,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000867</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000694</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00033</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00434</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.009228</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.002371</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000504</v>
       </c>
     </row>
     <row r="13">
@@ -1517,16 +1517,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.096024</v>
+        <v>-0.09515700000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.126168</v>
+        <v>-0.125474</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.919581</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.156809</v>
+        <v>-1.157139</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.368258</v>
@@ -1538,16 +1538,16 @@
         <v>-0.379766</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-7.246578</v>
+        <v>-7.242238</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.636801</v>
+        <v>-1.646029</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.840895</v>
+        <v>-1.843266</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.127298</v>
+        <v>-2.127802</v>
       </c>
     </row>
     <row r="28">
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.096024</v>
+        <v>-0.09515700000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.126168</v>
+        <v>-0.125474</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.919581</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.156809</v>
+        <v>-1.157139</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.368258</v>
@@ -1618,16 +1618,16 @@
         <v>-0.379766</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-7.246578</v>
+        <v>-7.242238</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.636801</v>
+        <v>-1.646029</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.840895</v>
+        <v>-1.843266</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.127298</v>
+        <v>-2.127802</v>
       </c>
     </row>
     <row r="30">
@@ -1835,10 +1835,10 @@
         <v>0.544478</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.252241</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.1501</v>
       </c>
     </row>
     <row r="35">
@@ -1915,10 +1915,10 @@
         <v>0.577091</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.052043</v>
+        <v>0.304284</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.034696</v>
+        <v>0.184796</v>
       </c>
     </row>
     <row r="37">
@@ -2395,10 +2395,10 @@
         <v>0.027443</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.266148</v>
+        <v>0.013907</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.584086</v>
+        <v>0.433986</v>
       </c>
     </row>
     <row r="49">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E330" s="5" t="n">
@@ -33162,7 +33162,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">

--- a/output/pdf_financials_xlsx/TUF.xlsx
+++ b/output/pdf_financials_xlsx/TUF.xlsx
@@ -3083,7 +3083,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.323712</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0.208267</v>
@@ -3188,25 +3188,25 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.070059</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.014695</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.03428</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.026493</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
@@ -5129,13 +5129,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.054375</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.081729</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.12517</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -17077,7 +17077,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -19321,7 +19325,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -24283,7 +24291,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -24423,7 +24435,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E260" s="5" t="n">
         <v>0.32249</v>
       </c>
@@ -25196,7 +25212,11 @@
           <t>Private placement 4,000,000</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -25821,7 +25841,11 @@
           <t>Private placement 9,458,332</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -26734,7 +26758,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E293" s="5" t="n">
         <v>0.0408</v>
       </c>
@@ -27160,7 +27188,11 @@
           <t>Fair value of warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E299" s="5" t="n">
         <v>0.0766</v>
       </c>
@@ -27229,7 +27261,11 @@
           <t>Fair value of broker warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -27515,7 +27551,11 @@
           <t>Private Placement 6,449,800</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E304" s="5" t="n">
         <v>0.32249</v>
       </c>
@@ -28006,7 +28046,11 @@
           <t>Private Placement 4,000,000</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E311" s="5" t="n">
         <v>0.2</v>
       </c>
